--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-ReferenceItemPrescription.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-ReferenceItemPrescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="100">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -293,14 +293,18 @@
     <t>ReferenceItemPrescription.traitementPrescrit</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/TraitementPrescrit
+</t>
+  </si>
+  <si>
+    <t>Traitement prescrit</t>
+  </si>
+  <si>
+    <t>ReferenceItemPrescription.reference</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base
 </t>
-  </si>
-  <si>
-    <t>Traitement prescrit</t>
-  </si>
-  <si>
-    <t>ReferenceItemPrescription.reference</t>
   </si>
   <si>
     <t>ID of parent container of referenced item</t>
@@ -630,7 +634,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.11328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1395,13 +1399,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1469,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1495,13 +1499,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1552,7 +1556,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1569,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1598,10 +1602,10 @@
         <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1652,7 +1656,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-ReferenceItemPrescription.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-ReferenceItemPrescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
